--- a/stories/arbres/ATOM-JEU.REG.002-01.xlsx
+++ b/stories/arbres/ATOM-JEU.REG.002-01.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Lila joue dans le jardin. Papa est là. Il y a un cerceau. Papa dit une règle. La règle : on attend. Puis on passe le cerceau. Lila écoute. Elle prend le cerceau trop vite. Papa va rappeler la règle une fois. Il dit : on attend. C'est la règle. Lila s'arrête. Elle attend. Puis elle passe le cerceau. Le cerceau glisse. Lila sourit. Papa dit : tu as suivi la règle. Lila répète : on attend. Une règle simple. Papa la rappelle. Lila la suit.</t>
+          <t>Lila joue dans le jardin. Papa est là. Il y a un cerceau. Papa dit une règle. La règle : on attend. Puis on passe le cerceau. Lila écoute. Elle prend le cerceau trop vite. Papa va rappeler la règle une fois. On attend. C'est la règle. Lila s'arrête. Elle attend. Puis elle passe le cerceau. Le cerceau glisse. Lila sourit. Tu as suivi la règle. Lila répète : on attend. Une règle simple. Papa la rappelle. Lila la suit.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Lila joue dans le jardin. Papa est là. Il y a un cerceau. Papa dit une règle. La règle : on attend. Puis on passe le cerceau. Lila écoute. Elle prend le cerceau trop vite. Papa va rappeler la règle une fois.
+narrateur|On attend. C'est la règle.
+narrateur|Lila s'arrête. Elle attend. Puis elle passe le cerceau. Le cerceau glisse. Lila sourit.
+papa|Tu as suivi la règle.
+narrateur|Lila répète : on attend. Une règle simple. Papa la rappelle. Lila la suit.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1494,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Lila joue. Que suit-elle ?</t>
         </is>
       </c>
     </row>
@@ -1637,6 +1667,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Lila a suivi la règle. Elle a attendu. Papa a rappelé une fois.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1799,6 +1834,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Lila pose le cerceau. Papa lui verse de l'eau.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1961,6 +2001,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1979,7 +2024,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1996,6 +2041,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-JEU.REG.002-01.xlsx
+++ b/stories/arbres/ATOM-JEU.REG.002-01.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,7 @@
 narrateur|Lila répète : on attend. Une règle simple. Papa la rappelle. Lila la suit.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1501,6 +1507,7 @@
           <t>narrateur|Lila joue. Que suit-elle ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1672,6 +1679,7 @@
           <t>narrateur|Lila a suivi la règle. Elle a attendu. Papa a rappelé une fois.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1839,6 +1847,7 @@
           <t>narrateur|Lila pose le cerceau. Papa lui verse de l'eau.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2006,6 +2015,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2024,7 +2034,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2048,6 +2058,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2062,7 +2086,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2249,6 +2273,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-JEU.REG.002-01.xlsx
+++ b/stories/arbres/ATOM-JEU.REG.002-01.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>La règle de Lila</t>
+          <t>Le cerceau jaune de Nina</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Après la pluie, Nina attend, puis passe le cerceau jaune. Papa rappelle la règle une fois.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Lila joue dans le jardin. Papa est là. Il y a un cerceau. Papa dit une règle. La règle : on attend. Puis on passe le cerceau. Lila écoute. Elle prend le cerceau trop vite. Papa va rappeler la règle une fois. On attend. C'est la règle. Lila s'arrête. Elle attend. Puis elle passe le cerceau. Le cerceau glisse. Lila sourit. Tu as suivi la règle. Lila répète : on attend. Une règle simple. Papa la rappelle. Lila la suit.</t>
+          <t>Le cerceau jaune s'appuie au grillage. L'herbe est encore mouillée. Elle brille un peu. Une abeille passe tout près. Elle s'en va. Les chaussures de Nina sont humides. Un oiseau chante derrière le mur. L'air sent la terre mouillée. Une goutte tombe de la gouttière. Elle fait un petit rond dans l'herbe. Un ver de terre glisse près de la clôture. Il s'en va, tout lent. Tu as vu le cerceau, Nina ? Oui, papa. Il est jaune. En ce moment, papa pose le cerceau. Le cerceau est lisse et froid. Une règle. On attend. Puis on passe le cerceau. J'ai envie d'y aller. On attend. Je te la rappelle. C'est la règle. Nina attend, les mains sur les genoux. Puis elle passe le cerceau. Le cerceau glisse un peu. Il glisse. Tu as suivi la règle. Tu as attendu. Bravo, Nina. On attend. Puis on passe. Oui. Une règle simple. Je la rappelle une fois. Nina passe encore le cerceau. L'herbe colle aux chaussures. Tu as suivi la règle dite. Bravo. Tu as fait du bon travail. Une règle. On attend. Oui. On la rappelle. Tu la suis. L'abeille est partie. Le grillage est encore humide. Encore une fois, tout doux ? Oui, papa. Nina attend. Puis elle passe le cerceau. Bravo. Tu as attendu. L'oiseau chante encore. J'ai suivi la règle. Oui. Une règle. On la rappelle. La goutte a fini de tomber. Tu as les pieds dans l'herbe ? Oui. Elle est mouillée. On attend, puis on passe. Bravo. Nina essuie une main sur son pantalon. L'herbe a laissé une trace verte. Le cerceau est encore au sol. Il est jaune. Il brille. Oui. Une règle. On attend. Nina pose les deux mains sur les genoux. Elle attend. Puis elle passe. Bravo. Tu as suivi la règle.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,14 +1324,67 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Lila joue dans le jardin. Papa est là. Il y a un cerceau. Papa dit une règle. La règle : on attend. Puis on passe le cerceau. Lila écoute. Elle prend le cerceau trop vite. Papa va rappeler la règle une fois.
-narrateur|On attend. C'est la règle.
-narrateur|Lila s'arrête. Elle attend. Puis elle passe le cerceau. Le cerceau glisse. Lila sourit.
+          <t>narrateur|Le cerceau jaune s'appuie au grillage.
+narrateur|L'herbe est encore mouillée.
+narrateur|Elle brille un peu.
+narrateur|Une abeille passe tout près.
+narrateur|Elle s'en va.
+narrateur|Les chaussures de Nina sont humides.
+narrateur|Un oiseau chante derrière le mur.
+narrateur|L'air sent la terre mouillée.
+narrateur|Une goutte tombe de la gouttière.
+narrateur|Elle fait un petit rond dans l'herbe.
+narrateur|Un ver de terre glisse près de la clôture.
+narrateur|Il s'en va, tout lent.
+papa|Tu as vu le cerceau, Nina ?
+enfant-f|Oui, papa. Il est jaune.
+narrateur|En ce moment, papa pose le cerceau.
+narrateur|Le cerceau est lisse et froid.
+papa|Une règle. On attend.
+papa|Puis on passe le cerceau.
+enfant-f|J'ai envie d'y aller.
+papa|On attend. Je te la rappelle.
+papa|C'est la règle.
+narrateur|Nina attend, les mains sur les genoux.
+narrateur|Puis elle passe le cerceau.
+narrateur|Le cerceau glisse un peu.
+enfant-f|Il glisse.
 papa|Tu as suivi la règle.
-narrateur|Lila répète : on attend. Une règle simple. Papa la rappelle. Lila la suit.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+papa|Tu as attendu. Bravo, Nina.
+enfant-f|On attend. Puis on passe.
+papa|Oui. Une règle simple.
+papa|Je la rappelle une fois.
+narrateur|Nina passe encore le cerceau.
+narrateur|L'herbe colle aux chaussures.
+papa|Tu as suivi la règle dite.
+papa|Bravo. Tu as fait du bon travail.
+enfant-f|Une règle. On attend.
+papa|Oui. On la rappelle. Tu la suis.
+narrateur|L'abeille est partie.
+narrateur|Le grillage est encore humide.
+papa|Encore une fois, tout doux ?
+enfant-f|Oui, papa.
+narrateur|Nina attend.
+narrateur|Puis elle passe le cerceau.
+papa|Bravo. Tu as attendu.
+narrateur|L'oiseau chante encore.
+enfant-f|J'ai suivi la règle.
+papa|Oui. Une règle. On la rappelle.
+narrateur|La goutte a fini de tomber.
+papa|Tu as les pieds dans l'herbe ?
+enfant-f|Oui. Elle est mouillée.
+papa|On attend, puis on passe. Bravo.
+narrateur|Nina essuie une main sur son pantalon.
+narrateur|L'herbe a laissé une trace verte.
+papa|Le cerceau est encore au sol.
+enfant-f|Il est jaune. Il brille.
+papa|Oui. Une règle. On attend.
+narrateur|Nina pose les deux mains sur les genoux.
+narrateur|Elle attend.
+narrateur|Puis elle passe.
+papa|Bravo. Tu as suivi la règle.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1344,7 +1409,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Lila joue. Que suit-elle ?</t>
+          <t>Nina joue. Que suit-elle ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1504,10 +1569,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Lila joue. Que suit-elle ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Nina joue.
+narrateur|Que suit-elle ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1532,7 +1597,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Lila a suivi la règle. Elle a attendu. Papa a rappelé une fois.</t>
+          <t>Nina a suivi la règle. Elle a attendu. Je t'ai rappelé une fois. Une règle. On attend. Oui. Bravo, Nina. Le cerceau repose contre le grillage.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1676,10 +1741,14 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Lila a suivi la règle. Elle a attendu. Papa a rappelé une fois.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Nina a suivi la règle.
+narrateur|Elle a attendu.
+papa|Je t'ai rappelé une fois.
+enfant-f|Une règle. On attend.
+papa|Oui. Bravo, Nina.
+narrateur|Le cerceau repose contre le grillage.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1704,7 +1773,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Lila pose le cerceau. Papa lui verse de l'eau.</t>
+          <t>Nina pose le cerceau. Tu veux un peu d'eau ? Oui, papa. Papa verse de l'eau. L'eau est fraîche. Merci. L'herbe brille encore. Le cerceau reste au grillage ? Oui. Il est jaune. Une goutte encore, tout loin.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1844,10 +1913,18 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Lila pose le cerceau. Papa lui verse de l'eau.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Nina pose le cerceau.
+papa|Tu veux un peu d'eau ?
+enfant-f|Oui, papa.
+narrateur|Papa verse de l'eau.
+narrateur|L'eau est fraîche.
+enfant-f|Merci.
+narrateur|L'herbe brille encore.
+papa|Le cerceau reste au grillage ?
+enfant-f|Oui. Il est jaune.
+narrateur|Une goutte encore, tout loin.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1872,7 +1949,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Nina tient la gourde, tout près. J'ai attendu. Oui. Tu as suivi la règle. Bravo, Nina. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2012,10 +2089,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Nina tient la gourde, tout près.
+enfant-f|J'ai attendu.
+papa|Oui. Tu as suivi la règle.
+papa|Bravo, Nina.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2034,7 +2114,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2072,6 +2152,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-JEU.REG.002-01.xlsx
+++ b/stories/arbres/ATOM-JEU.REG.002-01.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le cerceau jaune s'appuie au grillage. L'herbe est encore mouillée. Elle brille un peu. Une abeille passe tout près. Elle s'en va. Les chaussures de Nina sont humides. Un oiseau chante derrière le mur. L'air sent la terre mouillée. Une goutte tombe de la gouttière. Elle fait un petit rond dans l'herbe. Un ver de terre glisse près de la clôture. Il s'en va, tout lent. Tu as vu le cerceau, Nina ? Oui, papa. Il est jaune. En ce moment, papa pose le cerceau. Le cerceau est lisse et froid. Une règle. On attend. Puis on passe le cerceau. J'ai envie d'y aller. On attend. Je te la rappelle. C'est la règle. Nina attend, les mains sur les genoux. Puis elle passe le cerceau. Le cerceau glisse un peu. Il glisse. Tu as suivi la règle. Tu as attendu. Bravo, Nina. On attend. Puis on passe. Oui. Une règle simple. Je la rappelle une fois. Nina passe encore le cerceau. L'herbe colle aux chaussures. Tu as suivi la règle dite. Bravo. Tu as fait du bon travail. Une règle. On attend. Oui. On la rappelle. Tu la suis. L'abeille est partie. Le grillage est encore humide. Encore une fois, tout doux ? Oui, papa. Nina attend. Puis elle passe le cerceau. Bravo. Tu as attendu. L'oiseau chante encore. J'ai suivi la règle. Oui. Une règle. On la rappelle. La goutte a fini de tomber. Tu as les pieds dans l'herbe ? Oui. Elle est mouillée. On attend, puis on passe. Bravo. Nina essuie une main sur son pantalon. L'herbe a laissé une trace verte. Le cerceau est encore au sol. Il est jaune. Il brille. Oui. Une règle. On attend. Nina pose les deux mains sur les genoux. Elle attend. Puis elle passe. Bravo. Tu as suivi la règle.</t>
+          <t>Le cerceau jaune s'appuie au grillage. L'herbe est encore mouillée. Elle brille un peu. Une abeille passe tout près. Elle s'en va. Les chaussures de Nina sont humides. Un oiseau chante derrière le mur. L'air sent la terre mouillée. Une goutte tombe de la gouttière. Elle fait un petit rond dans l'herbe. Un ver de terre glisse près de la clôture. Il s'en va, tout lent. Tu as vu le cerceau, Nina ? Oui, papa. Il est jaune. En ce moment, papa pose le cerceau. Le cerceau est lisse et froid. Une règle. On attend. Puis on passe le cerceau. J'ai envie d'y aller. On attend. Je te la rappelle. C'est la règle. Nina attend, les mains sur les genoux. Puis elle passe le cerceau. Le cerceau glisse un peu. Il glisse. Tu as suivi la règle. Tu as attendu. Bravo, Nina. On attend. Puis on passe. Oui. Une règle simple. Je la rappelle une fois. Nina passe encore le cerceau. L'herbe colle aux chaussures. Tu as suivi la règle dite. Une règle. On attend. Oui. On la rappelle. Tu la suis. L'abeille est partie. Le grillage est encore humide. Encore une fois, tout doux ? Oui, papa. Nina attend. Puis elle passe le cerceau. Bravo. Tu as attendu. L'oiseau chante encore. J'ai suivi la règle. Oui. Une règle. On la rappelle. La goutte a fini de tomber. Tu as les pieds dans l'herbe ? Oui. Elle est mouillée. On attend, puis on passe. Bravo. Nina essuie une main sur son pantalon. L'herbe a laissé une trace verte. Le cerceau est encore au sol. Il est jaune. Il brille. Oui. Une règle. On attend. Nina pose les deux mains sur les genoux. Elle attend. Puis elle passe. Bravo. Tu as suivi la règle.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Lila joue dans le jardin. Papa est là. Il y a un cerceau. Papa dit &lt;emphasis level="moderate"&gt;une&lt;/emphasis&gt; règle. La règle : on attend. Puis on passe le cerceau. Lila écoute. Elle prend le cerceau trop vite. Papa va rappeler la règle une fois. Il dit : on attend. C'est la règle. Lila s'arrête. Elle attend. Puis elle passe le cerceau. Le cerceau glisse. Lila sourit. Papa dit : tu as suivi la règle. Lila répète : on attend. Une règle simple. Papa la rappelle. Lila la suit.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le cerceau jaune s'appuie au grillage. L'herbe est encore mouillée. Elle brille un peu. Une abeille passe tout près. Elle s'en va. Les chaussures de Nina sont humides. Un oiseau chante derrière le mur. L'air sent la terre mouillée. Une goutte tombe de la gouttière. Elle fait un petit rond dans l'herbe. Un ver de terre glisse près de la clôture. Il s'en va, tout lent. Tu as vu le cerceau, Nina ? Oui, papa. Il est jaune. En ce moment, papa pose le cerceau. Le cerceau est lisse et froid. Une règle. On attend. Puis on passe le cerceau. J'ai envie d'y aller. On attend. Je te la rappelle. C'est la règle. Nina attend, les mains sur les genoux. Puis elle passe le cerceau. Le cerceau glisse un peu. Il glisse. Tu as suivi la règle. Tu as attendu. Bravo, Nina. On attend. Puis on passe. Oui. Une règle simple. Je la rappelle une fois. Nina passe encore le cerceau. L'herbe colle aux chaussures. Tu as suivi la règle dite. Une règle. On attend. Oui. On la rappelle. Tu la suis. L'abeille est partie. Le grillage est encore humide. Encore une fois, tout doux ? Oui, papa. Nina attend. Puis elle passe le cerceau. Bravo. Tu as attendu. L'oiseau chante encore. J'ai suivi la règle. Oui. Une règle. On la rappelle. La goutte a fini de tomber. Tu as les pieds dans l'herbe ? Oui. Elle est mouillée. On attend, puis on passe. Bravo. Nina essuie une main sur son pantalon. L'herbe a laissé une trace verte. Le cerceau est encore au sol. Il est jaune. Il brille. Oui. Une règle. On attend. Nina pose les deux mains sur les genoux. Elle attend. Puis elle passe. Bravo. Tu as suivi la règle.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1357,7 +1357,6 @@
 narrateur|Nina passe encore le cerceau.
 narrateur|L'herbe colle aux chaussures.
 papa|Tu as suivi la règle dite.
-papa|Bravo. Tu as fait du bon travail.
 enfant-f|Une règle. On attend.
 papa|Oui. On la rappelle. Tu la suis.
 narrateur|L'abeille est partie.
@@ -1414,7 +1413,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Li&lt;emphasis level="moderate"&gt;la&lt;/emphasis&gt; joue. Que suit-elle ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nina joue. Que suit-elle ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1602,7 +1601,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Lila a suivi la règle. Elle a attendu. Papa a rappelé &lt;emphasis level="moderate"&gt;une&lt;/emphasis&gt; fois.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nina a suivi la règle. Elle a attendu. Je t'ai rappelé une fois. Une règle. On attend. Oui. Bravo, Nina. Le cerceau repose contre le grillage.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1778,7 +1777,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Li&lt;emphasis level="moderate"&gt;la&lt;/emphasis&gt; pose le cerceau. Papa lui verse de l'eau.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nina pose le cerceau. Tu veux un peu d'eau ? Oui, papa. Papa verse de l'eau. L'eau est fraîche. Merci. L'herbe brille encore. Le cerceau reste au grillage ? Oui. Il est jaune. Une goutte encore, tout loin.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1949,12 +1948,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Nina tient la gourde, tout près. J'ai attendu. Oui. Tu as suivi la règle. Bravo, Nina. L'histoire est finie.</t>
+          <t>Nina tient la gourde, tout près. J'ai attendu. Oui. Tu as suivi la règle. Bravo, Nina.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nina tient la gourde, tout près. J'ai attendu. Oui. Tu as suivi la règle. Bravo, Nina.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2092,8 +2091,7 @@
           <t>narrateur|Nina tient la gourde, tout près.
 enfant-f|J'ai attendu.
 papa|Oui. Tu as suivi la règle.
-papa|Bravo, Nina.
-narrateur|L'histoire est finie.</t>
+papa|Bravo, Nina.</t>
         </is>
       </c>
     </row>
@@ -2114,7 +2112,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2159,6 +2157,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-JEU.REG.002-01.xlsx
+++ b/stories/arbres/ATOM-JEU.REG.002-01.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>jardin</t>
+          <t>jardin mouillé, grillage, cerceau jaune</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Lila, papa</t>
+          <t>Nina, papa</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-JEU.REG.002-01.xlsx
+++ b/stories/arbres/ATOM-JEU.REG.002-01.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Le cerceau jaune de Nina</t>
+          <t>Le cerceau du figuier</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>jardin mouillé, grillage, cerceau jaune</t>
+          <t>jardin du village, figuier, après-midi d'été</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Nina, papa</t>
+          <t>Mila, papa</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Après la pluie, Nina attend, puis passe le cerceau jaune. Papa rappelle la règle une fois.</t>
+          <t>Mila veut passer dans le cerceau rouge du figuier. Elle tire trop vite, le cerceau tombe dans les haricots. Ils attendent un peu. Papa tient, elle passe. Le fruit sent encore.</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Le cerceau jaune s'appuie au grillage. L'herbe est encore mouillée. Elle brille un peu. Une abeille passe tout près. Elle s'en va. Les chaussures de Nina sont humides. Un oiseau chante derrière le mur. L'air sent la terre mouillée. Une goutte tombe de la gouttière. Elle fait un petit rond dans l'herbe. Un ver de terre glisse près de la clôture. Il s'en va, tout lent. Tu as vu le cerceau, Nina ? Oui, papa. Il est jaune. En ce moment, papa pose le cerceau. Le cerceau est lisse et froid. Une règle. On attend. Puis on passe le cerceau. J'ai envie d'y aller. On attend. Je te la rappelle. C'est la règle. Nina attend, les mains sur les genoux. Puis elle passe le cerceau. Le cerceau glisse un peu. Il glisse. Tu as suivi la règle. Tu as attendu. Bravo, Nina. On attend. Puis on passe. Oui. Une règle simple. Je la rappelle une fois. Nina passe encore le cerceau. L'herbe colle aux chaussures. Tu as suivi la règle dite. Une règle. On attend. Oui. On la rappelle. Tu la suis. L'abeille est partie. Le grillage est encore humide. Encore une fois, tout doux ? Oui, papa. Nina attend. Puis elle passe le cerceau. Bravo. Tu as attendu. L'oiseau chante encore. J'ai suivi la règle. Oui. Une règle. On la rappelle. La goutte a fini de tomber. Tu as les pieds dans l'herbe ? Oui. Elle est mouillée. On attend, puis on passe. Bravo. Nina essuie une main sur son pantalon. L'herbe a laissé une trace verte. Le cerceau est encore au sol. Il est jaune. Il brille. Oui. Une règle. On attend. Nina pose les deux mains sur les genoux. Elle attend. Puis elle passe. Bravo. Tu as suivi la règle.</t>
+          <t>Le figuier du jardin a des feuilles chaudes. Une abeille tourne tout près. Ça sent le fruit mûr. Le linge blanc sèche sur la corde. Il claque un peu, tout doux. La terre est sèche, un peu rose. Des haricots grimpent le long d'un fil. Le village est calme, derrière le mur. Mila, tu vois le cerceau ? Oui, papa. Il est rouge. Le cerceau est posé contre le figuier. Il brille un peu au soleil. En ce moment, Mila court vers lui. Je veux passer. Comme un tunnel. Moi je le tiens. Toi tu passes. Papa pose un pied près du bois. Il n'a pas encore les deux mains. Mila tire déjà le cerceau. Le cerceau penche. Il tombe. Toc. Il roule vers les haricots. Oh. Il part. Il est tombé. On attend un peu ? Mila s'arrête. L'abeille s'éloigne. Une feuille de figuier bouge. Le cerceau est dans les feuilles. Je le prends. Doucement. On y va ensemble. Ils marchent entre les haricots. Les feuilles frottent les genoux. Ça sent le vert, tout fort. Mila touche le cerceau. Le plastique est chaud, un peu poussiéreux. Je l'ai. On le ramène près de l'arbre. Papa tient le cerceau, cette fois. Ses deux mains sont dessus. Tu attends que je sois prêt ? Oui. On attend un peu. Mila reste les pieds dans la terre. Elle regarde le trou du cerceau. Le jardin est tout calme. L'abeille revient, tout bas.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Le cerceau jaune s'appuie au grillage. L'herbe est encore mouillée. Elle brille un peu. Une abeille passe tout près. Elle s'en va. Les chaussures de Nina sont humides. Un oiseau chante derrière le mur. L'air sent la terre mouillée. Une goutte tombe de la gouttière. Elle fait un petit rond dans l'herbe. Un ver de terre glisse près de la clôture. Il s'en va, tout lent. Tu as vu le cerceau, Nina ? Oui, papa. Il est jaune. En ce moment, papa pose le cerceau. Le cerceau est lisse et froid. Une règle. On attend. Puis on passe le cerceau. J'ai envie d'y aller. On attend. Je te la rappelle. C'est la règle. Nina attend, les mains sur les genoux. Puis elle passe le cerceau. Le cerceau glisse un peu. Il glisse. Tu as suivi la règle. Tu as attendu. Bravo, Nina. On attend. Puis on passe. Oui. Une règle simple. Je la rappelle une fois. Nina passe encore le cerceau. L'herbe colle aux chaussures. Tu as suivi la règle dite. Une règle. On attend. Oui. On la rappelle. Tu la suis. L'abeille est partie. Le grillage est encore humide. Encore une fois, tout doux ? Oui, papa. Nina attend. Puis elle passe le cerceau. Bravo. Tu as attendu. L'oiseau chante encore. J'ai suivi la règle. Oui. Une règle. On la rappelle. La goutte a fini de tomber. Tu as les pieds dans l'herbe ? Oui. Elle est mouillée. On attend, puis on passe. Bravo. Nina essuie une main sur son pantalon. L'herbe a laissé une trace verte. Le cerceau est encore au sol. Il est jaune. Il brille. Oui. Une règle. On attend. Nina pose les deux mains sur les genoux. Elle attend. Puis elle passe. Bravo. Tu as suivi la règle.</t>
+          <t>Le figuier du jardin a des feuilles chaudes. Une abeille tourne tout près. Ça sent le fruit mûr. Le linge blanc sèche sur la corde. Il claque un peu, tout doux. La terre est sèche, un peu rose. Des haricots grimpent le long d'un fil. Le village est calme, derrière le mur. Mila, tu vois le cerceau ? Oui, papa. Il est rouge. Le cerceau est posé contre le figuier. Il brille un peu au soleil. En ce moment, Mila court vers lui. Je veux passer. Comme un tunnel. Moi je le tiens. Toi tu passes. Papa pose un pied près du bois. Il n'a pas encore les deux mains. Mila tire déjà le cerceau. Le cerceau penche. Il tombe. Toc. Il roule vers les haricots. Oh. Il part. Il est tombé. On attend un peu ? Mila s'arrête. L'abeille s'éloigne. Une feuille de figuier bouge. Le cerceau est dans les feuilles. Je le prends. Doucement. On y va ensemble. Ils marchent entre les haricots. Les feuilles frottent les genoux. Ça sent le vert, tout fort. Mila touche le cerceau. Le plastique est chaud, un peu poussiéreux. Je l'ai. On le ramène près de l'arbre. Papa tient le cerceau, cette fois. Ses deux mains sont dessus. Tu attends que je sois prêt ? Oui. On attend un peu. Mila reste les pieds dans la terre. Elle regarde le trou du cerceau. Le jardin est tout calme. L'abeille revient, tout bas.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1245,14 +1245,14 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA2" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1324,64 +1324,58 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Le cerceau jaune s'appuie au grillage.
-narrateur|L'herbe est encore mouillée.
-narrateur|Elle brille un peu.
-narrateur|Une abeille passe tout près.
-narrateur|Elle s'en va.
-narrateur|Les chaussures de Nina sont humides.
-narrateur|Un oiseau chante derrière le mur.
-narrateur|L'air sent la terre mouillée.
-narrateur|Une goutte tombe de la gouttière.
-narrateur|Elle fait un petit rond dans l'herbe.
-narrateur|Un ver de terre glisse près de la clôture.
-narrateur|Il s'en va, tout lent.
-papa|Tu as vu le cerceau, Nina ?
-enfant-f|Oui, papa. Il est jaune.
-narrateur|En ce moment, papa pose le cerceau.
-narrateur|Le cerceau est lisse et froid.
-papa|Une règle. On attend.
-papa|Puis on passe le cerceau.
-enfant-f|J'ai envie d'y aller.
-papa|On attend. Je te la rappelle.
-papa|C'est la règle.
-narrateur|Nina attend, les mains sur les genoux.
-narrateur|Puis elle passe le cerceau.
-narrateur|Le cerceau glisse un peu.
-enfant-f|Il glisse.
-papa|Tu as suivi la règle.
-papa|Tu as attendu. Bravo, Nina.
-enfant-f|On attend. Puis on passe.
-papa|Oui. Une règle simple.
-papa|Je la rappelle une fois.
-narrateur|Nina passe encore le cerceau.
-narrateur|L'herbe colle aux chaussures.
-papa|Tu as suivi la règle dite.
-enfant-f|Une règle. On attend.
-papa|Oui. On la rappelle. Tu la suis.
-narrateur|L'abeille est partie.
-narrateur|Le grillage est encore humide.
-papa|Encore une fois, tout doux ?
+          <t>narrateur|Le figuier du jardin a des feuilles chaudes.
+narrateur|Une abeille tourne tout près.
+narrateur|Ça sent le fruit mûr.
+narrateur|Le linge blanc sèche sur la corde.
+narrateur|Il claque un peu, tout doux.
+narrateur|La terre est sèche, un peu rose.
+narrateur|Des haricots grimpent le long d'un fil.
+narrateur|Le village est calme, derrière le mur.
+papa|Mila, tu vois le cerceau ?
 enfant-f|Oui, papa.
-narrateur|Nina attend.
-narrateur|Puis elle passe le cerceau.
-papa|Bravo. Tu as attendu.
-narrateur|L'oiseau chante encore.
-enfant-f|J'ai suivi la règle.
-papa|Oui. Une règle. On la rappelle.
-narrateur|La goutte a fini de tomber.
-papa|Tu as les pieds dans l'herbe ?
-enfant-f|Oui. Elle est mouillée.
-papa|On attend, puis on passe. Bravo.
-narrateur|Nina essuie une main sur son pantalon.
-narrateur|L'herbe a laissé une trace verte.
-papa|Le cerceau est encore au sol.
-enfant-f|Il est jaune. Il brille.
-papa|Oui. Une règle. On attend.
-narrateur|Nina pose les deux mains sur les genoux.
-narrateur|Elle attend.
-narrateur|Puis elle passe.
-papa|Bravo. Tu as suivi la règle.</t>
+enfant-f|Il est rouge.
+narrateur|Le cerceau est posé contre le figuier.
+narrateur|Il brille un peu au soleil.
+narrateur|En ce moment, Mila court vers lui.
+enfant-f|Je veux passer.
+enfant-f|Comme un tunnel.
+papa|Moi je le tiens.
+papa|Toi tu passes.
+narrateur|Papa pose un pied près du bois.
+narrateur|Il n'a pas encore les deux mains.
+narrateur|Mila tire déjà le cerceau.
+narrateur|Le cerceau penche.
+narrateur|Il tombe.
+narrateur|Toc.
+narrateur|Il roule vers les haricots.
+enfant-f|Oh.
+enfant-f|Il part.
+papa|Il est tombé.
+papa|On attend un peu ?
+narrateur|Mila s'arrête.
+narrateur|L'abeille s'éloigne.
+narrateur|Une feuille de figuier bouge.
+narrateur|Le cerceau est dans les feuilles.
+enfant-f|Je le prends.
+papa|Doucement.
+papa|On y va ensemble.
+narrateur|Ils marchent entre les haricots.
+narrateur|Les feuilles frottent les genoux.
+narrateur|Ça sent le vert, tout fort.
+narrateur|Mila touche le cerceau.
+narrateur|Le plastique est chaud, un peu poussiéreux.
+enfant-f|Je l'ai.
+papa|On le ramène près de l'arbre.
+narrateur|Papa tient le cerceau, cette fois.
+narrateur|Ses deux mains sont dessus.
+papa|Tu attends que je sois prêt ?
+enfant-f|Oui.
+papa|On attend un peu.
+narrateur|Mila reste les pieds dans la terre.
+narrateur|Elle regarde le trou du cerceau.
+narrateur|Le jardin est tout calme.
+narrateur|L'abeille revient, tout bas.</t>
         </is>
       </c>
     </row>
@@ -1408,12 +1402,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Nina joue. Que suit-elle ?</t>
+          <t>Mila veut passer. Que fait-elle d'abord ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Nina joue. Que suit-elle ?</t>
+          <t>Mila veut passer. Que fait-elle d'abord ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1423,12 +1417,12 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>la règle</t>
+          <t>attendre</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>la règle | une règle | attendre | on attend</t>
+          <t>attendre | on attend | un peu | son tour | elle attend | il attend | attendre un peu | on attend un peu | à son tour</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1443,7 +1437,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Papa la dit encore. C'est quoi ?</t>
+          <t>Elle reste un peu. Que fait Mila d'abord ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1492,7 +1486,7 @@
         <v>0.8</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1568,8 +1562,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Nina joue.
-narrateur|Que suit-elle ?</t>
+          <t>narrateur|Mila veut passer.
+narrateur|Que fait-elle d'abord ?</t>
         </is>
       </c>
     </row>
@@ -1596,12 +1590,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Nina a suivi la règle. Elle a attendu. Je t'ai rappelé une fois. Une règle. On attend. Oui. Bravo, Nina. Le cerceau repose contre le grillage.</t>
+          <t>Mila reste encore un peu. J'ai les deux mains. Tu peux passer. J'y vais. Elle plie les genoux. Elle passe dans le trou rouge. Le cerceau ne bouge pas. Il tient, tout rond. Je suis passée ! Oui. Il est resté debout. Mila se retourne. Le figuier fait une ombre ronde. Une figue sent très fort. Encore une fois ? Encore. On attend un peu. Papa replace le cerceau. Mila compte dans sa tête. Un. Deux. Maintenant. Elle passe encore. Ses cheveux touchent le plastique. Merci, Mila. C'est un tunnel.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Nina a suivi la règle. Elle a attendu. Je t'ai rappelé une fois. Une règle. On attend. Oui. Bravo, Nina. Le cerceau repose contre le grillage.</t>
+          <t>Mila reste encore un peu. J'ai les deux mains. Tu peux passer. J'y vais. Elle plie les genoux. Elle passe dans le trou rouge. Le cerceau ne bouge pas. Il tient, tout rond. Je suis passée ! Oui. Il est resté debout. Mila se retourne. Le figuier fait une ombre ronde. Une figue sent très fort. Encore une fois ? Encore. On attend un peu. Papa replace le cerceau. Mila compte dans sa tête. Un. Deux. Maintenant. Elle passe encore. Ses cheveux touchent le plastique. Merci, Mila. C'est un tunnel.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1657,14 +1651,14 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA4" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1740,12 +1734,32 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Nina a suivi la règle.
-narrateur|Elle a attendu.
-papa|Je t'ai rappelé une fois.
-enfant-f|Une règle. On attend.
-papa|Oui. Bravo, Nina.
-narrateur|Le cerceau repose contre le grillage.</t>
+          <t>narrateur|Mila reste encore un peu.
+papa|J'ai les deux mains.
+papa|Tu peux passer.
+enfant-f|J'y vais.
+narrateur|Elle plie les genoux.
+narrateur|Elle passe dans le trou rouge.
+narrateur|Le cerceau ne bouge pas.
+narrateur|Il tient, tout rond.
+enfant-f|Je suis passée !
+papa|Oui.
+papa|Il est resté debout.
+narrateur|Mila se retourne.
+narrateur|Le figuier fait une ombre ronde.
+narrateur|Une figue sent très fort.
+papa|Encore une fois ?
+enfant-f|Encore.
+papa|On attend un peu.
+narrateur|Papa replace le cerceau.
+narrateur|Mila compte dans sa tête.
+narrateur|Un.
+narrateur|Deux.
+papa|Maintenant.
+narrateur|Elle passe encore.
+narrateur|Ses cheveux touchent le plastique.
+papa|Merci, Mila.
+enfant-f|C'est un tunnel.</t>
         </is>
       </c>
     </row>
@@ -1772,12 +1786,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Nina pose le cerceau. Tu veux un peu d'eau ? Oui, papa. Papa verse de l'eau. L'eau est fraîche. Merci. L'herbe brille encore. Le cerceau reste au grillage ? Oui. Il est jaune. Une goutte encore, tout loin.</t>
+          <t>On va boire ? J'ai chaud. La pompe du jardin est froide. Papa verse de l'eau. Ça fait un petit bruit. Mila boit. Une goutte tombe sur le pied. Elle est froide. Le cerceau attend encore. Je repasse ? Oui. Quand je tiens bien. Ils reviennent sous le figuier. Le linge claque, plus loin. Papa lève le cerceau. Mila attend, les mains ouvertes. Tu es prête ? Oui, papa. Elle passe tout droit. Le plastique reste chaud. L'abeille tourne autour d'une figue. Elle me regarde. Elle aussi, elle attend.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Nina pose le cerceau. Tu veux un peu d'eau ? Oui, papa. Papa verse de l'eau. L'eau est fraîche. Merci. L'herbe brille encore. Le cerceau reste au grillage ? Oui. Il est jaune. Une goutte encore, tout loin.</t>
+          <t>On va boire ? J'ai chaud. La pompe du jardin est froide. Papa verse de l'eau. Ça fait un petit bruit. Mila boit. Une goutte tombe sur le pied. Elle est froide. Le cerceau attend encore. Je repasse ? Oui. Quand je tiens bien. Ils reviennent sous le figuier. Le linge claque, plus loin. Papa lève le cerceau. Mila attend, les mains ouvertes. Tu es prête ? Oui, papa. Elle passe tout droit. Le plastique reste chaud. L'abeille tourne autour d'une figue. Elle me regarde. Elle aussi, elle attend.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1833,14 +1847,14 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA5" s="2" t="n">
         <v>0.86</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1912,16 +1926,29 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Nina pose le cerceau.
-papa|Tu veux un peu d'eau ?
+          <t>papa|On va boire ?
+enfant-f|J'ai chaud.
+narrateur|La pompe du jardin est froide.
+narrateur|Papa verse de l'eau.
+narrateur|Ça fait un petit bruit.
+narrateur|Mila boit.
+narrateur|Une goutte tombe sur le pied.
+enfant-f|Elle est froide.
+papa|Le cerceau attend encore.
+enfant-f|Je repasse ?
+papa|Oui.
+papa|Quand je tiens bien.
+narrateur|Ils reviennent sous le figuier.
+narrateur|Le linge claque, plus loin.
+narrateur|Papa lève le cerceau.
+narrateur|Mila attend, les mains ouvertes.
+papa|Tu es prête ?
 enfant-f|Oui, papa.
-narrateur|Papa verse de l'eau.
-narrateur|L'eau est fraîche.
-enfant-f|Merci.
-narrateur|L'herbe brille encore.
-papa|Le cerceau reste au grillage ?
-enfant-f|Oui. Il est jaune.
-narrateur|Une goutte encore, tout loin.</t>
+narrateur|Elle passe tout droit.
+narrateur|Le plastique reste chaud.
+narrateur|L'abeille tourne autour d'une figue.
+enfant-f|Elle me regarde.
+papa|Elle aussi, elle attend.</t>
         </is>
       </c>
     </row>
@@ -1948,12 +1975,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Nina tient la gourde, tout près. J'ai attendu. Oui. Tu as suivi la règle. Bravo, Nina.</t>
+          <t>Le tunnel est rouge. Et toi, tu es passée. Bravo, Mila. Le figuier sent encore le fruit. Le cerceau tient contre le tronc.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Nina tient la gourde, tout près. J'ai attendu. Oui. Tu as suivi la règle. Bravo, Nina.</t>
+          <t>Le tunnel est rouge. Et toi, tu es passée. Bravo, Mila. Le figuier sent encore le fruit. Le cerceau tient contre le tronc.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2009,14 +2036,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
         <v>0.82</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2088,10 +2115,11 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|Nina tient la gourde, tout près.
-enfant-f|J'ai attendu.
-papa|Oui. Tu as suivi la règle.
-papa|Bravo, Nina.</t>
+          <t>enfant-f|Le tunnel est rouge.
+papa|Et toi, tu es passée.
+papa|Bravo, Mila.
+narrateur|Le figuier sent encore le fruit.
+narrateur|Le cerceau tient contre le tronc.</t>
         </is>
       </c>
     </row>
@@ -2112,7 +2140,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2162,6 +2190,13 @@
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
